--- a/artfynd/A 62010-2022 artfynd.xlsx
+++ b/artfynd/A 62010-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62010-2022 artfynd.xlsx
+++ b/artfynd/A 62010-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4028055</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400698.5970712038</v>
+        <v>400699</v>
       </c>
       <c r="R2" t="n">
-        <v>6602877.346153353</v>
+        <v>6602877</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1982-08-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1982-08-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
